--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{246F9E97-CE38-42E9-84F5-C480DDF1B8A9}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6D517EEC-1196-4147-A4A7-B1BFC75DAAE0}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -87,6 +87,18 @@
   </si>
   <si>
     <t>Automation test description</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
   </si>
 </sst>
 </file>
@@ -422,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
@@ -485,6 +497,48 @@
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6D517EEC-1196-4147-A4A7-B1BFC75DAAE0}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{56688E0F-7E93-4522-9E43-9A7E1B28580C}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -44,61 +44,64 @@
     <t>ProgramName__c</t>
   </si>
   <si>
+    <t>Dropdown</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>Project Grants</t>
+  </si>
+  <si>
+    <t>Lookup</t>
+  </si>
+  <si>
+    <t>PrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>Research And Innovative Technology Administration</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Abbreviation__c</t>
+  </si>
+  <si>
+    <t>WebsiteAddress__c</t>
+  </si>
+  <si>
+    <t>http://automate.com</t>
+  </si>
+  <si>
+    <t>Objectives__c</t>
+  </si>
+  <si>
+    <t>RichText</t>
+  </si>
+  <si>
+    <t>Automation test description</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>AuPr</t>
+  </si>
+  <si>
     <t>Automation Program</t>
-  </si>
-  <si>
-    <t>Dropdown</t>
-  </si>
-  <si>
-    <t>Type__c</t>
-  </si>
-  <si>
-    <t>Project Grants</t>
-  </si>
-  <si>
-    <t>Lookup</t>
-  </si>
-  <si>
-    <t>PrimaryFundingOrganization__c</t>
-  </si>
-  <si>
-    <t>Research And Innovative Technology Administration</t>
-  </si>
-  <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Abbreviation__c</t>
-  </si>
-  <si>
-    <t>AuPr</t>
-  </si>
-  <si>
-    <t>WebsiteAddress__c</t>
-  </si>
-  <si>
-    <t>http://automate.com</t>
-  </si>
-  <si>
-    <t>Objectives__c</t>
-  </si>
-  <si>
-    <t>RichText</t>
-  </si>
-  <si>
-    <t>Automation test description</t>
-  </si>
-  <si>
-    <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>KPIsRequired__c</t>
-  </si>
-  <si>
-    <t>IsGoalsRequired__c</t>
   </si>
 </sst>
 </file>
@@ -468,7 +471,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -476,13 +479,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -490,13 +493,13 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -504,13 +507,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -518,13 +521,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -532,13 +535,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -573,44 +576,44 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{56688E0F-7E93-4522-9E43-9A7E1B28580C}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{99704BF7-2F35-46A9-8D5E-3B4490928DA6}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>IsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>AuPr</t>
@@ -471,7 +468,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -527,7 +524,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -541,7 +538,7 @@
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -585,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{99704BF7-2F35-46A9-8D5E-3B4490928DA6}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{50A2D09D-EE85-4CA4-A36E-AA09F8E0518A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
@@ -95,10 +95,10 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>AuPr</t>
-  </si>
-  <si>
     <t>Automation Program</t>
+  </si>
+  <si>
+    <t>AP</t>
   </si>
 </sst>
 </file>
@@ -468,7 +468,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{50A2D09D-EE85-4CA4-A36E-AA09F8E0518A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{A1CA3C76-A10A-4400-B2A7-38FC765DCB83}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
@@ -95,10 +95,10 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>Automation Program</t>
-  </si>
-  <si>
-    <t>AP</t>
+    <t>APTD</t>
+  </si>
+  <si>
+    <t>Automation Program to be deleted</t>
   </si>
 </sst>
 </file>
@@ -468,7 +468,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{A1CA3C76-A10A-4400-B2A7-38FC765DCB83}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{42D01BF8-1997-40C7-A603-11603953252E}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
@@ -95,10 +95,10 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>APTD</t>
-  </si>
-  <si>
-    <t>Automation Program to be deleted</t>
+    <t>Automation Program Dec10</t>
+  </si>
+  <si>
+    <t>AD10</t>
   </si>
 </sst>
 </file>
@@ -435,15 +435,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -468,10 +468,10 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -485,7 +485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -499,7 +499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -513,7 +513,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -527,7 +527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -550,14 +550,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,7 +571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -582,10 +582,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -599,7 +599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{42D01BF8-1997-40C7-A603-11603953252E}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{5A290231-AA61-4D9C-89C9-7E6A4C457033}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>PrimaryFundingOrganization__c</t>
   </si>
   <si>
-    <t>Research And Innovative Technology Administration</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>AD10</t>
+  </si>
+  <si>
+    <t>District Court</t>
   </si>
 </sst>
 </file>
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -151,7 +151,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -468,7 +467,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -495,8 +494,8 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
+      <c r="D4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,10 +506,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -524,7 +523,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -535,15 +534,18 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" tooltip="District Court" display="https://test7-internal--c.na57.visual.force.com/0010b00002CmKfwAAF" xr:uid="{855A68A3-A67F-4F57-8D11-7EF523E82526}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -573,44 +575,44 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{5A290231-AA61-4D9C-89C9-7E6A4C457033}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6F709890-6D22-4A03-80EC-69E38A267F95}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
     <t>AD10</t>
   </si>
   <si>
-    <t>District Court</t>
+    <t>Test Automation Organization</t>
   </si>
 </sst>
 </file>
@@ -541,11 +541,8 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" tooltip="District Court" display="https://test7-internal--c.na57.visual.force.com/0010b00002CmKfwAAF" xr:uid="{855A68A3-A67F-4F57-8D11-7EF523E82526}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{6F709890-6D22-4A03-80EC-69E38A267F95}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{06858BDE-AE39-46B8-8CEA-7C1860D99B4B}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
-    <sheet name="RequiredForSubmit" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="RequiredForSubmit" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -433,110 +434,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -547,6 +526,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{06858BDE-AE39-46B8-8CEA-7C1860D99B4B}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{EBCE6438-80F0-4970-8C53-BB621D14EC4C}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RequiredForSave" sheetId="3" r:id="rId1"/>
+    <sheet name="Creation" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
-    <sheet name="RequiredForSubmit" sheetId="4" r:id="rId3"/>
+    <sheet name="Edition" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -527,43 +527,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -575,73 +588,60 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{EBCE6438-80F0-4970-8C53-BB621D14EC4C}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{788EDFA5-56FA-419E-8BEA-878ABFC6EA00}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,13 +93,13 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>Automation Program Dec10</t>
-  </si>
-  <si>
-    <t>AD10</t>
-  </si>
-  <si>
     <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>Automation Program Dec25</t>
+  </si>
+  <si>
+    <t>AD25</t>
   </si>
 </sst>
 </file>
@@ -461,7 +461,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -483,7 +483,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -614,7 +614,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{788EDFA5-56FA-419E-8BEA-878ABFC6EA00}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{E50D0840-DD54-412F-A3D7-6FF37DB08079}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>Automation Program Dec25</t>
-  </si>
-  <si>
-    <t>AD25</t>
+    <t>Automation Program Jan 9 2019</t>
+  </si>
+  <si>
+    <t>AUJA</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{E50D0840-DD54-412F-A3D7-6FF37DB08079}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A4E90B-832E-4C4D-8174-726DCFF21F0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>Automation Program Jan 9 2019</t>
-  </si>
-  <si>
-    <t>AUJA</t>
+    <t>Automation Program Jan 16 2019</t>
+  </si>
+  <si>
+    <t>JA16</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A4E90B-832E-4C4D-8174-726DCFF21F0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D8B658-915E-43B5-9DF0-32CB679C25D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,10 +96,10 @@
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>Automation Program Jan 16 2019</t>
-  </si>
-  <si>
-    <t>JA16</t>
+    <t>Automation Program Jan 18 2019</t>
+  </si>
+  <si>
+    <t>JA18</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D8B658-915E-43B5-9DF0-32CB679C25D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915DD8EF-4BEE-4E0F-9BCB-1D91D263190C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>Test Automation Organization</t>
   </si>
   <si>
-    <t>Automation Program Jan 18 2019</t>
-  </si>
-  <si>
-    <t>JA18</t>
+    <t>JAId</t>
+  </si>
+  <si>
+    <t>Automation Program EGMS chk</t>
   </si>
 </sst>
 </file>
@@ -461,7 +461,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -614,7 +614,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915DD8EF-4BEE-4E0F-9BCB-1D91D263190C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684040CA-50B2-49B8-928A-5F4C05738D80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -42,64 +42,64 @@
     <t>None</t>
   </si>
   <si>
+    <t>Dropdown</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>Project Grants</t>
+  </si>
+  <si>
+    <t>Lookup</t>
+  </si>
+  <si>
+    <t>PrimaryFundingOrganization__c</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Abbreviation__c</t>
+  </si>
+  <si>
+    <t>WebsiteAddress__c</t>
+  </si>
+  <si>
+    <t>http://automate.com</t>
+  </si>
+  <si>
+    <t>Objectives__c</t>
+  </si>
+  <si>
+    <t>RichText</t>
+  </si>
+  <si>
+    <t>Automation test description</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Dropdown</t>
-  </si>
-  <si>
-    <t>Type__c</t>
-  </si>
-  <si>
-    <t>Project Grants</t>
-  </si>
-  <si>
-    <t>Lookup</t>
-  </si>
-  <si>
-    <t>PrimaryFundingOrganization__c</t>
-  </si>
-  <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Abbreviation__c</t>
-  </si>
-  <si>
-    <t>WebsiteAddress__c</t>
-  </si>
-  <si>
-    <t>http://automate.com</t>
-  </si>
-  <si>
-    <t>Objectives__c</t>
-  </si>
-  <si>
-    <t>RichText</t>
-  </si>
-  <si>
-    <t>Automation test description</t>
-  </si>
-  <si>
-    <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>KPIsRequired__c</t>
-  </si>
-  <si>
-    <t>IsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>JAId</t>
-  </si>
-  <si>
-    <t>Automation Program EGMS chk</t>
+    <t>Automation Program Jan19</t>
+  </si>
+  <si>
+    <t>JA19</t>
   </si>
 </sst>
 </file>
@@ -457,11 +457,11 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -469,10 +469,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -480,10 +480,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -491,10 +491,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -502,10 +502,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -513,10 +513,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -552,7 +552,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -560,25 +560,25 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -608,35 +608,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684040CA-50B2-49B8-928A-5F4C05738D80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340E094F-86C6-4C07-AA22-DE4C3039EF7C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Automation Program Jan19</t>
-  </si>
-  <si>
-    <t>JA19</t>
+    <t>JAVi</t>
+  </si>
+  <si>
+    <t>Automation Program Jan19 Vi</t>
   </si>
 </sst>
 </file>
@@ -461,7 +461,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -614,7 +614,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340E094F-86C6-4C07-AA22-DE4C3039EF7C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D0834A-CE7E-42FF-886E-3826546489C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -90,16 +90,10 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
+    <t>JAVi</t>
+  </si>
+  <si>
     <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>ProgramName__c</t>
-  </si>
-  <si>
-    <t>JAVi</t>
-  </si>
-  <si>
-    <t>Automation Program Jan19 Vi</t>
   </si>
 </sst>
 </file>
@@ -434,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -457,11 +451,11 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
+      <c r="B2" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -469,10 +463,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -480,10 +474,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -491,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -502,26 +496,18 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -614,7 +600,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D0834A-CE7E-42FF-886E-3826546489C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3A0E2F-F594-40DA-890D-C8430D6B61BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>ProgramName__c</t>
+  </si>
+  <si>
+    <t>Automation Program Jan21</t>
   </si>
 </sst>
 </file>
@@ -428,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -451,11 +457,11 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -463,10 +469,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -474,10 +480,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -485,7 +491,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -496,15 +502,26 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3A0E2F-F594-40DA-890D-C8430D6B61BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4FAF61-CC85-4AE8-89C9-D12BECB678A4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -90,16 +90,16 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>JAVi</t>
-  </si>
-  <si>
     <t>Test Automation Organization</t>
   </si>
   <si>
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Automation Program Jan21</t>
+    <t>Automation Program Jan25</t>
+  </si>
+  <si>
+    <t>JA25</t>
   </si>
 </sst>
 </file>
@@ -458,10 +458,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -483,7 +483,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -617,7 +617,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3A0E2F-F594-40DA-890D-C8430D6B61BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AE193D-D374-49A7-88B0-67B55D38EF60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -90,16 +90,16 @@
     <t>IsGoalsRequired__c</t>
   </si>
   <si>
-    <t>JAVi</t>
-  </si>
-  <si>
     <t>Test Automation Organization</t>
   </si>
   <si>
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Automation Program Jan21</t>
+    <t>Automation Program  Surya</t>
+  </si>
+  <si>
+    <t>JASN</t>
   </si>
 </sst>
 </file>
@@ -458,10 +458,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -483,7 +483,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,8 +594,9 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -617,7 +618,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4FAF61-CC85-4AE8-89C9-D12BECB678A4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2995F46-40D7-456F-873A-2525895F5919}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Automation Program Jan25</t>
-  </si>
-  <si>
-    <t>JA25</t>
+    <t>Automation Program Regression</t>
+  </si>
+  <si>
+    <t>PREG</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2995F46-40D7-456F-873A-2525895F5919}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153688CB-BFFA-45CB-BB21-969FA91651C1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -96,10 +96,10 @@
     <t>ProgramName__c</t>
   </si>
   <si>
-    <t>Automation Program Regression</t>
-  </si>
-  <si>
     <t>PREG</t>
+  </si>
+  <si>
+    <t>Automation Program Jan4</t>
   </si>
 </sst>
 </file>
@@ -461,7 +461,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -617,7 +617,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153688CB-BFFA-45CB-BB21-969FA91651C1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD68A65-28DA-4F68-B9B8-ACEBA9EA4529}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Program Jan4</t>
+    <t>Automation Program Jan5</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD68A65-28DA-4F68-B9B8-ACEBA9EA4529}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2BBCF4-F75D-4B6E-98AA-3AE7B6AE0DE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Program Jan5</t>
+    <t>Automation Program Feb15</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2BBCF4-F75D-4B6E-98AA-3AE7B6AE0DE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B0F7FC-A05D-482D-8BB7-31566910D95E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Program Feb15</t>
+    <t>Automation Program Regression</t>
   </si>
 </sst>
 </file>
@@ -435,14 +435,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -475,7 +475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -486,7 +486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -497,7 +497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -508,7 +508,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -531,13 +531,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -561,7 +561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -569,17 +569,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -592,13 +592,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -620,7 +620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B0F7FC-A05D-482D-8BB7-31566910D95E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCB5E0B-9F5F-47CA-814A-C88EA82A979C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Program Regression</t>
+    <t>Automation Program  Regression</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCB5E0B-9F5F-47CA-814A-C88EA82A979C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6501002D-26E1-4D98-8265-AB57804412A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Program  Regression</t>
+    <t>Automation Program Regression</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6501002D-26E1-4D98-8265-AB57804412A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D70266-6E80-4EC8-AE43-9BA141BD09AD}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Program Regression</t>
+    <t xml:space="preserve">Automation Program </t>
   </si>
 </sst>
 </file>
@@ -435,14 +435,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -475,7 +475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -486,7 +486,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -497,7 +497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -508,7 +508,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -531,13 +531,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -553,7 +553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -561,7 +561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -569,17 +569,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -592,13 +592,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -620,7 +620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D70266-6E80-4EC8-AE43-9BA141BD09AD}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C53632-E711-4317-8958-6FEFC1C94AFB}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,14 +99,14 @@
     <t>PREG</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Program </t>
+    <t>Execution Internal Program for Automation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +121,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00396B"/>
+      <name val="Helvetica"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,7 +150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -153,6 +159,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -460,7 +467,7 @@
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21425"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C53632-E711-4317-8958-6FEFC1C94AFB}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B1638-09EF-4EEF-98EC-F7C2552B98A6}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Execution Internal Program for Automation</t>
+    <t xml:space="preserve"> Automation Permanent Internal Program</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21425"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B1638-09EF-4EEF-98EC-F7C2552B98A6}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA467748-67B6-48E8-97DD-3A2A3D76F570}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>PREG</t>
   </si>
   <si>
-    <t xml:space="preserve"> Automation Permanent Internal Program</t>
+    <t>Automation Execution Internal Program</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21629"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA467748-67B6-48E8-97DD-3A2A3D76F570}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1781294-047C-4EE0-A08E-DACA844ACFA1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1781294-047C-4EE0-A08E-DACA844ACFA1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56107D6-46CF-46CD-A74D-D0C2BB2EAFED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,12 +121,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00396B"/>
-      <name val="Helvetica"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -159,7 +153,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -467,7 +460,7 @@
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>25</v>
       </c>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22325"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56107D6-46CF-46CD-A74D-D0C2BB2EAFED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494479CE-0ACE-41F9-B30A-1539C40988BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2846" yWindow="2846" windowWidth="16457" windowHeight="8554" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
-    <sheet name="Edition" sheetId="4" r:id="rId3"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId2"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Edition" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -100,6 +102,18 @@
   </si>
   <si>
     <t>Automation Execution Internal Program</t>
+  </si>
+  <si>
+    <t>Community Health &amp; Equity</t>
+  </si>
+  <si>
+    <t>Automation Execution Internal Program in another ORG</t>
+  </si>
+  <si>
+    <t>fieldAccount__c</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -435,14 +449,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,7 +467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -475,7 +489,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -486,7 +500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -497,7 +511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -508,7 +522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -529,59 +543,157 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -589,16 +701,77 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -620,7 +793,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -631,7 +804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22624"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494479CE-0ACE-41F9-B30A-1539C40988BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584600C8-A284-453B-A399-1BA0CBA64176}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2846" yWindow="2846" windowWidth="16457" windowHeight="8554" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>PREG</t>
   </si>
   <si>
-    <t>Automation Execution Internal Program</t>
-  </si>
-  <si>
     <t>Community Health &amp; Equity</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Automation Internal Program</t>
   </si>
 </sst>
 </file>
@@ -475,7 +475,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -570,7 +570,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
@@ -633,7 +633,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -682,7 +682,7 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -693,7 +693,7 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22624"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584600C8-A284-453B-A399-1BA0CBA64176}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DD5277-E5F0-4877-BA27-FF3527AB08BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -104,16 +104,16 @@
     <t>Community Health &amp; Equity</t>
   </si>
   <si>
-    <t>Automation Execution Internal Program in another ORG</t>
-  </si>
-  <si>
     <t>fieldAccount__c</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Automation Internal Program</t>
+    <t>Automation Runtime Internal Program</t>
+  </si>
+  <si>
+    <t>Automation Runtime Execution Internal Program in another ORG</t>
   </si>
 </sst>
 </file>
@@ -475,7 +475,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -548,7 +548,7 @@
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -570,7 +570,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -633,7 +633,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
@@ -682,7 +682,7 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -693,7 +693,7 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DD5277-E5F0-4877-BA27-FF3527AB08BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B041ACD-DF6A-4BD4-8AE6-506A95369509}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -449,14 +449,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,7 +467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -478,7 +478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -489,7 +489,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -500,7 +500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -511,7 +511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -522,7 +522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -545,13 +545,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -573,7 +573,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -584,7 +584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -595,7 +595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -606,7 +606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -617,7 +617,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -628,7 +628,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -645,14 +645,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -674,7 +674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -685,7 +685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -704,13 +704,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -726,7 +726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -734,7 +734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -742,17 +742,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -765,13 +765,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="17.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -782,7 +782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -793,7 +793,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -804,7 +804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B041ACD-DF6A-4BD4-8AE6-506A95369509}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC4929F-FE99-433D-8D37-63E64D17F57A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -13,6 +13,8 @@
     <sheet name="Edition1" sheetId="7" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
     <sheet name="Edition" sheetId="4" r:id="rId5"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId6"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -114,6 +116,18 @@
   </si>
   <si>
     <t>Automation Runtime Execution Internal Program in another ORG</t>
+  </si>
+  <si>
+    <t>fieldAbbreviation__c</t>
+  </si>
+  <si>
+    <t>Automation Program</t>
+  </si>
+  <si>
+    <t>Test With Automation PM</t>
+  </si>
+  <si>
+    <t>fieldObjectives__c</t>
   </si>
 </sst>
 </file>
@@ -822,4 +836,111 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC4929F-FE99-433D-8D37-63E64D17F57A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC8274D-C262-40F3-A76F-B6E970B6521A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC8274D-C262-40F3-A76F-B6E970B6521A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2579753B-369F-449F-800F-45ADA26253A4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>fieldObjectives__c</t>
+  </si>
+  <si>
+    <t>fieldEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -545,6 +548,17 @@
       </c>
       <c r="C7" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2579753B-369F-449F-800F-45ADA26253A4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277A8AF0-CAA0-4B57-8F7F-4FDFF321741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>fieldObjectives__c</t>
-  </si>
-  <si>
-    <t>fieldEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -465,15 +462,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -495,7 +492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -506,7 +503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -517,7 +514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -528,7 +525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -539,7 +536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -548,17 +545,6 @@
       </c>
       <c r="C7" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -573,13 +559,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -601,7 +587,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -612,7 +598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -623,7 +609,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -634,7 +620,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -645,7 +631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -656,7 +642,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -673,14 +659,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -702,7 +688,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -713,7 +699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -732,13 +718,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -746,7 +732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -754,7 +740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -762,7 +748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -770,17 +756,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -793,13 +779,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -821,7 +807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -832,7 +818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -855,14 +841,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,7 +859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -884,7 +870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -895,7 +881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -906,7 +892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -925,14 +911,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -943,7 +929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,18 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277A8AF0-CAA0-4B57-8F7F-4FDFF321741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1EC6C8-70BB-4B5A-AF8C-AB022EAFD6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId2"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
-    <sheet name="Edition" sheetId="4" r:id="rId5"/>
-    <sheet name="NGOCreation" sheetId="8" r:id="rId6"/>
-    <sheet name="NGOEdit" sheetId="9" r:id="rId7"/>
+    <sheet name="Creation2" sheetId="10" r:id="rId2"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId3"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Edition" sheetId="4" r:id="rId6"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId7"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -557,6 +558,100 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{832EB4E6-689C-4A9F-9F20-5BF3E0292CEF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -656,7 +751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -715,7 +810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -776,7 +871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -838,7 +933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -908,7 +1003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1EC6C8-70BB-4B5A-AF8C-AB022EAFD6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Creation" sheetId="3" r:id="rId1"/>
-    <sheet name="Creation2" sheetId="10" r:id="rId2"/>
-    <sheet name="Creation1" sheetId="6" r:id="rId3"/>
-    <sheet name="Edition1" sheetId="7" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
-    <sheet name="Edition" sheetId="4" r:id="rId6"/>
-    <sheet name="NGOCreation" sheetId="8" r:id="rId7"/>
-    <sheet name="NGOEdit" sheetId="9" r:id="rId8"/>
+    <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
+    <sheet name="Creation" sheetId="3" r:id="rId2"/>
+    <sheet name="Creation2" sheetId="10" r:id="rId3"/>
+    <sheet name="Creation1" sheetId="6" r:id="rId4"/>
+    <sheet name="Edition1" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
+    <sheet name="Edition" sheetId="4" r:id="rId7"/>
+    <sheet name="NGOCreation" sheetId="8" r:id="rId8"/>
+    <sheet name="NGOEdit" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -129,6 +130,9 @@
   </si>
   <si>
     <t>fieldObjectives__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Internal Program For Bulk Records</t>
   </si>
 </sst>
 </file>
@@ -462,6 +466,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{E44E2E55-A2EC-4DFF-AAA5-2623A48FE502}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -557,7 +655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -651,7 +749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -751,7 +849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -810,7 +908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -871,7 +969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -933,7 +1031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1003,7 +1101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA2FCAF-B95A-46FB-A7E9-45920F6C38FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -66,73 +66,73 @@
     <t>Overview</t>
   </si>
   <si>
+    <t>RichText</t>
+  </si>
+  <si>
+    <t>Automation test description</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>ProgramName__c</t>
+  </si>
+  <si>
+    <t>Community Health &amp; Equity</t>
+  </si>
+  <si>
+    <t>fieldAccount__c</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Automation Runtime Internal Program</t>
+  </si>
+  <si>
+    <t>Automation Runtime Execution Internal Program in another ORG</t>
+  </si>
+  <si>
+    <t>fieldAbbreviation__c</t>
+  </si>
+  <si>
+    <t>Automation Program</t>
+  </si>
+  <si>
+    <t>Test With Automation PM</t>
+  </si>
+  <si>
+    <t>fieldObjectives__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Internal Program For Bulk Records</t>
+  </si>
+  <si>
+    <t>Objectives__c</t>
+  </si>
+  <si>
     <t>Abbreviation__c</t>
   </si>
   <si>
+    <t>PREG</t>
+  </si>
+  <si>
     <t>WebsiteAddress__c</t>
   </si>
   <si>
     <t>http://automate.com</t>
-  </si>
-  <si>
-    <t>Objectives__c</t>
-  </si>
-  <si>
-    <t>RichText</t>
-  </si>
-  <si>
-    <t>Automation test description</t>
-  </si>
-  <si>
-    <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>KPIsRequired__c</t>
-  </si>
-  <si>
-    <t>IsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>ProgramName__c</t>
-  </si>
-  <si>
-    <t>PREG</t>
-  </si>
-  <si>
-    <t>Community Health &amp; Equity</t>
-  </si>
-  <si>
-    <t>fieldAccount__c</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Automation Runtime Internal Program</t>
-  </si>
-  <si>
-    <t>Automation Runtime Execution Internal Program in another ORG</t>
-  </si>
-  <si>
-    <t>fieldAbbreviation__c</t>
-  </si>
-  <si>
-    <t>Automation Program</t>
-  </si>
-  <si>
-    <t>Test With Automation PM</t>
-  </si>
-  <si>
-    <t>fieldObjectives__c</t>
-  </si>
-  <si>
-    <t>Automation Runtime Internal Program For Bulk Records</t>
   </si>
 </sst>
 </file>
@@ -468,13 +468,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2C26CE-2E8C-4867-AC56-9F8B4DB5FDCF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,18 +485,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -507,7 +507,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -515,40 +515,40 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -562,14 +562,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,18 +580,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -602,7 +602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -610,40 +610,40 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -658,13 +658,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55179DDA-4361-4F07-BFD1-9218C77D4E2C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,18 +675,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -697,7 +697,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -705,40 +705,40 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -752,13 +752,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6001F8-9503-4627-8A30-24CC2F7D5FB4}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,18 +769,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -791,7 +791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -799,48 +799,48 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -852,14 +852,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{331D5782-8D69-43BD-93B1-6E246548F8D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,37 +870,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -911,13 +911,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -925,7 +925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -933,7 +933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -941,25 +941,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -972,13 +972,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,59 +989,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{2964AC08-382B-4FAE-8F45-970C952B4A4E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9955554F-DF1E-411E-8C5F-ECCA28DE187F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,18 +1049,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1074,26 +1071,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1104,14 +1101,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AE1456-E3FC-4FDA-BF72-5437A679B596}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,15 +1119,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
